--- a/extenbooks/XS1601.xlsx
+++ b/extenbooks/XS1601.xlsx
@@ -809,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_validated</t>
+          <t>pending:faithful_kt_source</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Status**: CULLED (do not publish) — fabricated proxy, 2026-06-11 reconciliation</t>
+          <t>**Status**: pending:faithful_kt_source</t>
         </is>
       </c>
     </row>
@@ -1022,19 +1022,23 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>40 rows 1980-2019. Range [47.99%, 56.77%].</t>
+          <t>&gt; CULLED / DO NOT PUBLISH (`publish: false`, `triage.verdict: cull`). The `pending:faithful_kt_source`</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>&gt; status reconciles this DPR with the registry (WP-E review 2026-07-01): the prior registry</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**CORRECTION (2026-06-11)**: The prior claim that this "approximately matches K&amp;T's</t>
+          <t>&gt; `book_period_validated` was a FALSE validation claim — V03 "passes" only against tautological</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1046,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>reported labor share trajectory" is FALSE. The chopped data RISES from 0.480 (1980) to</t>
+          <t>&gt; reference_values (the proxy's own output) under a 0.15 mean-tolerance that masks the divergence.</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1054,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.553 (2019), whereas Karabacak &amp; Tonak (2022, Section 5.8) report labour share</t>
+          <t>&gt; The series is a World-Bank value-added proxy, blocked pending faithful re-derivation from K&amp;T 2022's</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1062,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DECLINING from 45.3% (1980) to 35.2% (2019). The series is NOT K&amp;T's labour share and</t>
+          <t>&gt; own construction (see `triage.republish_condition`). T6b attempt = BLOCKED-G2 (K&amp;T publish no annual</t>
         </is>
       </c>
     </row>
@@ -1066,61 +1070,117 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NOT the TurkStat Table 20.37 compensation data the research JSON claims: the code</t>
+          <t>&gt; labour-share table; paper paywalled). Old status: `book_period_validated`.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>(`P02_XS1601_turkey_labor_share.py`) computes `(industry_va_pct_gdp + 0.5 *</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>services_va_pct_gdp) / 100` from World Bank structural indicators — a value-added proxy</t>
+          <t>40 rows 1980-2019. Range [47.99%, 56.77%].</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>in violation of the No-Proxies mandate. Culled pending re-derivation from the paper's</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>actual labour-share series or from faithful TurkStat compensation data.</t>
+          <t>**CORRECTION (2026-06-11)**: The prior claim that this "approximately matches K&amp;T's</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>reported labor share trajectory" is FALSE. The chopped data RISES from 0.480 (1980) to</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>0.553 (2019), whereas Karabacak &amp; Tonak (2022, Section 5.8) report labour share</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DECLINING from 45.3% (1980) to 35.2% (2019). The series is NOT K&amp;T's labour share and</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
+        <is>
+          <t>NOT the TurkStat Table 20.37 compensation data the research JSON claims: the code</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>(`P02_XS1601_turkey_labor_share.py`) computes `(industry_va_pct_gdp + 0.5 *</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>services_va_pct_gdp) / 100` from World Bank structural indicators — a value-added proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>in violation of the No-Proxies mandate. Culled pending re-derivation from the paper's</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>actual labour-share series or from faithful TurkStat compensation data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1137,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1175,7 +1235,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1252,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1269,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1286,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1303,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1320,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1294,109 +1354,109 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>definition</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Labor share (ls) is defined as V / (V + S) = wages of productive workers / Net Domestic Product. In the Karabacak &amp; Tonak (2022) operational framework, V = total compensation of employees minus unproductive workers' wages, and V + S = Net Domestic Product at factor cost. Unproductive sectors excluded from V include: wholesale and retail trade, finance and insurance, real estate, professional/administrative services, public administration and defense, private education, and private health services. Productive sectors included: agriculture, forestry, mining, manufacturing, utilities, construction, transportation, accommodation/food services, information/communication.</t>
+          <t>K&amp;T 2022 report labour share (ls = V/(V+S)) ONLY as an aggregate over 1980-2019 and as an internal input to Figures 7-11; the paper prints NO annual labour-share table. Independent K&amp;T anchor (KB Statistical Summary reconstructed from the paper): ls mean 39.7%, std 3.2%, min 34.8%, max 45.3%, declining ~45% (1980) to ~35% (2019). NOTE: the CULLED World-Bank value-added proxy in XS1601 RISES 0.480 (1980) -&gt; 0.553 (2019) with mean 0.540 - diverging from this anchor in BOTH level and direction, confirming it is not K&amp;T's labour share.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KT_2022, Section 4.4; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>Karabacak &amp; Tonak 2022, RRPE 54(4):479-500, Statistical Summary (ls mean 39.7%, min 34.8%, max 45.3%) + Methodological Notes ('Turkey 1980-2019 range: 35-45% ... declining trend')</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>data_source_primary</t>
+          <t>definition</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TurkStat Table 20.37 — 'Share of Gross Domestic Product by cost components (at current prices)' — provides compensation_of_employees_share as percent of GDP for 1980-2006 (27 annual observations). This is the income-approach GDP decomposition from TurkStat Statistical Indicators 1923-2011, Chapter 20 (National Accounts), digitized via HDARP from chunk_027 of turkstat_indicators_1923_2011.pdf. The column 'compensation_of_employees_share' gives the economy-wide wage share at current prices, directly comparable to the labor share denominator used in KT (2022).</t>
+          <t>Labor share (ls) is defined as V / (V + S) = wages of productive workers / Net Domestic Product. In the Karabacak &amp; Tonak (2022) operational framework, V = total compensation of employees minus unproductive workers' wages, and V + S = Net Domestic Product at factor cost. Unproductive sectors excluded from V include: wholesale and retail trade, finance and insurance, real estate, professional/administrative services, public administration and defense, private education, and private health services. Productive sectors included: agriculture, forestry, mining, manufacturing, utilities, construction, transportation, accommodation/food services, information/communication.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv</t>
+          <t>KT_2022, Section 4.4; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>data_values</t>
+          <t>data_source_primary</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Selected annual compensation_of_employees_share (% of GDP) from TurkStat Table 20.37: 1980=27.1, 1981=23.8, 1982=22.5, 1983=23.4, 1984=21.0, 1985=19.7. The full series runs 1980-2006. The chunk_027_summary notes: 'Compensation of employees (labor share): 27.1% in 1980, declined through 1980s to ~19-20%, rose again through 1990s crisis to 31.9% in 1991, then trended down to 26.2% by 2006.' This declining trend reflects union suppression, labor market deregulation, and informalization — consistent with KT (2022) Section 5.8 which reports ls ranging ~35-45% over 1980-2019.</t>
+          <t>TurkStat Table 20.37 — 'Share of Gross Domestic Product by cost components (at current prices)' — provides compensation_of_employees_share as percent of GDP for 1980-2006 (27 annual observations). This is the income-approach GDP decomposition from TurkStat Statistical Indicators 1923-2011, Chapter 20 (National Accounts), digitized via HDARP from chunk_027 of turkstat_indicators_1923_2011.pdf. The column 'compensation_of_employees_share' gives the economy-wide wage share at current prices, directly comparable to the labor share denominator used in KT (2022).</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv (first 10 lines); Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md</t>
+          <t>Inputs/ST2/Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; Inputs/ST2/Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>paper_benchmarks</t>
+          <t>data_values</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karabacak &amp; Tonak (2022) Section 5.8 report labor share over time: 1980=45.3%, 1990=42.7%, 2000=40.1%, 2010=37.5%, 2019=35.2%. Total decline: 10.1 percentage points (1980-2019). Note: the paper's ls values (from productive sector wages / NDP) are systematically higher than TurkStat Table 20.37's compensation_of_employees / GDP because (a) NDP &lt; GDP (excludes capital consumption) and (b) total compensation includes unproductive sectors which are partially subtracted in the paper's numerator. The TurkStat series provides the official national accounts anchor; the paper's full productive/unproductive decomposition methodology requires disaggregated sector-level employment and wage data not available in Table 20.37.</t>
+          <t>Selected annual compensation_of_employees_share (% of GDP) from TurkStat Table 20.37: 1980=27.1, 1981=23.8, 1982=22.5, 1983=23.4, 1984=21.0, 1985=19.7. The full series runs 1980-2006. The chunk_027_summary notes: 'Compensation of employees (labor share): 27.1% in 1980, declined through 1980s to ~19-20%, rose again through 1990s crisis to 31.9% in 1991, then trended down to 26.2% by 2006.' This declining trend reflects union suppression, labor market deregulation, and informalization — consistent with KT (2022) Section 5.8 which reports ls ranging ~35-45% over 1980-2019.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KT_2022, Section 5.8; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>Inputs/ST2/Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv (first 10 lines); Inputs/ST2/Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>data_gap</t>
+          <t>paper_benchmarks</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coverage is 1980-2006 only. TurkStat Statistical Indicators 1923-2011 does NOT publish income-approach GDP decomposition tables for 2007 onward (chunk_027_summary confirms this is the final chunk of Chapter 20, ending at 2006). Years 2007-2019 are NaN per [internal-decision-record] (no-synthetic-data policy). No synthetic fill, interpolation, or proxy substitution is permissible. The 2007-2019 gap means XS1601 has 27 real observations (1980-2006) and 13 NaN years (2007-2019).</t>
+          <t>Karabacak &amp; Tonak (2022) Section 5.8 report labor share over time: 1980=45.3%, 1990=42.7%, 2000=40.1%, 2010=37.5%, 2019=35.2%. Total decline: 10.1 percentage points (1980-2019). Note: the paper's ls values (from productive sector wages / NDP) are systematically higher than TurkStat Table 20.37's compensation_of_employees / GDP because (a) NDP &lt; GDP (excludes capital consumption) and (b) total compensation includes unproductive sectors which are partially subtracted in the paper's numerator. The TurkStat series provides the official national accounts anchor; the paper's full productive/unproductive decomposition methodology requires disaggregated sector-level employment and wage data not available in Table 20.37.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; [internal-decision-log]#[internal-decision-record]; [internal-decision-log]#[internal-decision-record]</t>
+          <t>KT_2022, Section 5.8; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>data_gap</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[internal-decision-record] (2026-05-06): XS1601 now uses TurkStat national accounts data (Table 20.37: compensation of employees as % of GDP, 1980-2006) extracted via HDARP. The previous SBB 'Personel' budget expenditure share proxy is removed. The SBB Personel share measured government personnel spending as a fraction of total government expenditure — structurally different from the economy-wide labor share (compensation of all employees / GDP). TurkStat Table 20.37 is the official income-approach decomposition, directly comparable to the KT (2022) methodology.</t>
+          <t>Coverage is 1980-2006 only. TurkStat Statistical Indicators 1923-2011 does NOT publish income-approach GDP decomposition tables for 2007 onward (chunk_027_summary confirms this is the final chunk of Chapter 20, ending at 2006). Years 2007-2019 are NaN per [internal-decision-record] (no-synthetic-data policy). No synthetic fill, interpolation, or proxy substitution is permissible. The 2007-2019 gap means XS1601 has 27 real observations (1980-2006) and 13 NaN years (2007-2019).</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[internal-decision-log]#[internal-decision-record]</t>
+          <t>Inputs/ST2/Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; [internal-decision-log]#[internal-decision-record]; [internal-decision-log]#[internal-decision-record]</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1468,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[internal-decision-record] (2026-05-03): Strict no-synthetic-data rule. XS1601 was previously listed as 'synthetic' (linear trend from HDARP benchmarks, np.random). This is prohibited. Real data is available from TurkStat Table 20.37 (1980-2006). Years 2007-2019 cannot be filled synthetically; they must be NaN. If real data for the 2007-2019 period is later obtained (e.g., from TurkStat NACE Rev.2 national accounts), it must be extracted via HDARP or API and documented with full provenance.</t>
+          <t>[internal-decision-record] (2026-05-06): XS1601 now uses TurkStat national accounts data (Table 20.37: compensation of employees as % of GDP, 1980-2006) extracted via HDARP. The previous SBB 'Personel' budget expenditure share proxy is removed. The SBB Personel share measured government personnel spending as a fraction of total government expenditure — structurally different from the economy-wide labor share (compensation of all employees / GDP). TurkStat Table 20.37 is the official income-approach decomposition, directly comparable to the KT (2022) methodology.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1420,46 +1480,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[internal-decision-record] (2026-05-03): Strict no-synthetic-data rule. XS1601 was previously listed as 'synthetic' (linear trend from HDARP benchmarks, np.random). This is prohibited. Real data is available from TurkStat Table 20.37 (1980-2006). Years 2007-2019 cannot be filled synthetically; they must be NaN. If real data for the 2007-2019 period is later obtained (e.g., from TurkStat NACE Rev.2 national accounts), it must be extracted via HDARP or API and documented with full provenance.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>methodology_note</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Labor share is used in the NSW calculation as the allocation parameter for mixed expenditures and taxes: B = E1 + E2*ls and T = T1 + T2*ls. A declining labor share mechanically worsens NSW even if tax rates and spending ratios are unchanged, because workers bear a larger share of indirect taxes (T2*ls falls more slowly than ls) and receive a smaller share of mixed benefits (E2*ls shrinks). KT (2022) Section 5.8 quantifies this: if ls had remained at the 1980 level (45%), NSW in 2019 would have been -1.8% instead of the actual -2.3% of GDP — labor share decline accounts for 0.5 pp of worsening.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>KT_2022, Sections 3.5 and 5.8; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>KT_2022, Sections 3.5 and 5.8; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>XS1601 uses TurkStat Table 20.37 compensation_of_employees_share (% of GDP) for 1980-2006 as the primary data source, replacing the prior synthetic SBB proxy ([internal-decision-record]). Years 2007-2019 are NaN per [internal-decision-record]. The series is expressed as a decimal share (divide CSV percent by 100). It serves as the labor-share allocation parameter ls in the NSW calculation for XS1602.</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CULLED (2026-06-11 reconciliation): this research JSON attributes the series to TurkStat Table 20.37 compensation data, but the implemented code (P02_XS1601_turkey_labor_share.py) uses a World Bank value-added proxy (industry_va + 0.5*services_va)/100. The chopped data rises 0.480-&gt;0.553 (1980-2019), contradicting both the claimed TurkStat source and K&amp;T's published declining labour share (45.3%-&gt;35.2%). No-Proxies violation. Series culled; do not publish.</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1536,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2007-2019 gap: TurkStat Statistical Indicators 1923-2011 does not cover post-2006 income-approach tables. Years 2007-2019 are NaN per [internal-decision-record].</t>
+          <t>CULLED (2026-06-11 reconciliation): this research JSON attributes the series to TurkStat Table 20.37 compensation data, but the implemented code (P02_XS1601_turkey_labor_share.py) uses a World Bank value-added proxy (industry_va + 0.5*services_va)/100. The chopped data rises 0.480-&gt;0.553 (1980-2019), contradicting both the claimed TurkStat source and K&amp;T's published declining labour share (45.3%-&gt;35.2%). No-Proxies violation. Series culled; do not publish.</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1544,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TurkStat Table 20.37 gives total compensation / GDP (economy-wide). KT (2022) uses productive-sector wages / NDP, so levels will differ systematically. The TurkStat series is the best available official anchor for 1980-2006.</t>
+          <t>2007-2019 gap: TurkStat Statistical Indicators 1923-2011 does not cover post-2006 income-approach tables. Years 2007-2019 are NaN per [internal-decision-record].</t>
         </is>
       </c>
     </row>
@@ -1483,53 +1552,61 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
+          <t>TurkStat Table 20.37 gives total compensation / GDP (economy-wide). KT (2022) uses productive-sector wages / NDP, so levels will differ systematically. The TurkStat series is the best available official anchor for 1980-2006.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Pre-2006 data quality: KT (2022) Section 4.6 notes Turkey's fiscal and national accounts statistics improved significantly after 2006 (IMF-mandated reforms); pre-2006 data required reconciliation across sources.</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>cross_references:</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
         <is>
           <t>XS1602</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KT_2022</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Karabacak, Zafer, and E. Ahmet Tonak. 2022. 'The Net Social Wage in Turkey, 1980-2019.' Review of Radical Political Economics 54 (4): 577-605. DOI: 10.1177/04866134221089659.</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>KT_2022</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Karabacak, Yakup, and E. Ahmet Tonak. 2022. 'The Net Social Wage in Turkey, 1980-2019.' Review of Radical Political Economics 54 (4): 577-605. DOI: 10.1177/04866134221089659.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>TurkStat_2011</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Turkish Statistical Institute (TurkStat). 2011. Statistical Indicators 1923-2011. Table 20.37: Share of Gross Domestic Product by cost components (at current prices), 1980-2006. Ankara: TurkStat. [Digitized via HDARP, chunk_027.]</t>
         </is>
@@ -1546,7 +1623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1706,6 +1783,18 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>validator_class</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>tautological</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/XS1601.xlsx
+++ b/extenbooks/XS1601.xlsx
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inputs/ST2/Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; Inputs/ST2/Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv</t>
+          <t>data/raw/Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; data/raw/Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inputs/ST2/Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv (first 10 lines); Inputs/ST2/Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md</t>
+          <t>data/raw/Technical/Knowledge_Base/turkstat_indicators_1923_2011/CSV_Tables/chunk_027_table03_GDP_income_approach_shares_pct_1980_2006.csv (first 10 lines); data/raw/Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inputs/ST2/Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; [internal-decision-log]#[internal-decision-record]; [internal-decision-log]#[internal-decision-record]</t>
+          <t>data/raw/Technical/Knowledge_Base/turkstat_indicators_1923_2011/chunk_027_summary.md; [internal-decision-log]#[internal-decision-record]; [internal-decision-log]#[internal-decision-record]</t>
         </is>
       </c>
     </row>
